--- a/kv_cache_prefill_data.xlsx
+++ b/kv_cache_prefill_data.xlsx
@@ -14,7 +14,11 @@
     <sheet name="Inference Frameworks" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Agent Workloads" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="GPU Memory Budget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cost Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="HBM Supply-Demand" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GPU HBM Requirements" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Installed Base Memory" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="KV Cache Scenarios" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cost Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -935,6 +939,815 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AI GPUs (M equiv.)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Avg HBM/GPU (GB)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Inference Share (%)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Avg Ctx Used (K tok)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Avg Concurrent/GPU</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Total HBM (EB)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Inference HBM (EB)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Est. KV Cache VRAM (EB)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GPU Growth (YoY)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>KV Demand Growth (YoY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>150</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" t="n">
+        <v>67</v>
+      </c>
+      <c r="E5" t="n">
+        <v>64</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>87</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Weights (GB)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>KV Cache (GB)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Total (GB)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>KV %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Llama 70B
+4K ctx × 1 user</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Llama 70B
+128K ctx × 1 user</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3" t="n">
+        <v>112</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Llama 70B
+128K ctx × 8 users</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="n">
+        <v>336</v>
+      </c>
+      <c r="D4" t="n">
+        <v>406</v>
+      </c>
+      <c r="E4" t="n">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gemini-class
+1M ctx × 1 user</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>200</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E5" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Llama 4 Maverick
+128K × 16 users</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>400</v>
+      </c>
+      <c r="C6" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>803.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2
+128K × 64 users</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>685</v>
+      </c>
+      <c r="C7" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>832.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cache Hit Rate</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cost per Request ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1575</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.12375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0441</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.02925</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.6</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0225</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0915</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.079</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.059</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0565</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GPT-4.1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0675</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.05344</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.03938</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.02813</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.02025</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.01688</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.01406</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Pro</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.01125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.01421</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.01106</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.00791</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.00539</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.00363</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.00287</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.00224</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.00161</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2586,440 +3399,345 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cache Hit Rate</t>
+          <t>HBM Supply (B GB)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cost per Request ($)</t>
+          <t>HBM Demand (B GB)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>HBM Revenue ($B)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Gap (B GB)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Shortage %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-7.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7000000000000002</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C8" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" t="n">
+        <v>160</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>HBM Capacity (GB)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>HBM Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Bandwidth (TB/s)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Est. Price/GPU ($K)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>HBM Cost Share (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>A100 (2020)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.1575</v>
+        <v>80</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HBM2e</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>H100 (2022)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.12375</v>
+        <v>80</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HBM3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>H200 (2024)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.09</v>
+        <v>141</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HBM3e</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>B200 (2025)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.063</v>
+        <v>192</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HBM3e</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>B300 (2025)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0441</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Claude Sonnet 4.6</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Claude Sonnet 4.6</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.02925</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Claude Sonnet 4.6</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0225</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.104</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0915</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.079</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.062</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.059</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.0565</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GPT-4.1</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.054</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.0675</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.05344</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.03938</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.02813</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.02025</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.01688</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.01406</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Pro</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.01125</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.01421</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.01106</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.00791</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.00539</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.00363</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.00287</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.00224</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DeepSeek V3.2</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.00161</v>
+        <v>288</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HBM3e</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/kv_cache_prefill_data.xlsx
+++ b/kv_cache_prefill_data.xlsx
@@ -18,7 +18,9 @@
     <sheet name="GPU HBM Requirements" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Installed Base Memory" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="KV Cache Scenarios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Cost Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Agent KV Comparison" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Multi-Turn Cost Model" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Cost Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1307,6 +1309,878 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OpenClaw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Claude Cowork</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Perplexity Computer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CONTEXT STRUCTURE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>System Prompt Baseline</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>~8–10K tokens (core instructions, SOUL.md,
+AGENTS.md, tool schemas, skills metadata).
+Full bootstrap with workspace files:
+~40K tokens before any user input.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>~78K tokens average per request
+(system instructions + file contents +
+conversation history + tool definitions).
+99.4% of tokens are input; 0.6% output.
+166:1 input-to-output ratio.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Varies per sub-model. Meta-router
+allocates task to one of 19 models.
+Each model receives task-specific context,
+not a monolithic system prompt.
+Agent API replaces MCP to avoid
+72% context waste from tool schemas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bootstrap File Budget</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Max 150K chars total across all bootstrap
+files (SOUL.md, AGENTS.md, TOOLS.md,
+IDENTITY.md, USER.md, MEMORY.md, etc.).
+Per-file cap: 20K chars default.
+Inspectable via /context list command.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>No equivalent bootstrap system.
+Context built from:
+  • System prompt
+  • Tool definitions
+  • Conversation history
+  • File contents (injected on demand)
+Max context: 200K (Sonnet/Opus)
+or 1M (Max extended plans).</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No bootstrap files.
+E2B Linux sandbox provides filesystem.
+Sub-agents share filesystem but have
+no memory access between invocations.
+Context is task-scoped, not session-scoped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Context Growth Pattern</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3–5 turns with tool calls → 80–90K tokens.
+5-turn chat costs 13× single-turn
+(full history re-sent each message).
+200K token default context window.
+ContextEngine plugin provides 7 lifecycle
+hooks for custom context management.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Grows to fill context window.
+Auto-compaction at ~70% capacity
+frees 60–70% of space.
+Quality degrades past 70% utilization.
+Pre/PostCompact hooks available.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Task-scoped: each sub-agent call
+is relatively independent.
+Meta-router decomposes complex tasks
+into smaller model calls.
+No single context window grows
+to extreme sizes — but total tokens
+across all sub-calls can be very high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KV CACHE BEHAVIOR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cache Hit Rate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>KNOWN BUG: Dynamic prompt variations
+(timestamps, channel metadata, tool results)
+invalidate prefix between turns.
+Creates multiple cached prompt entries
+rather than reusing one.
+Estimated: significantly below 84%.
+Issues #45110, #40256, #27732 track this.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BEST-IN-CLASS: 84% average cache hit rate.
+Up to 96% in optimized single sessions.
+Agent teams/swarms: 97.2% aggregate
+cache hit across 4 Opus teammates.
+Strict byte-exact prefix matching
+(any byte change invalidates downstream).</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>STRUCTURALLY LOW (estimated):
+Multi-model routing means each task
+may hit a different provider's cache.
+Model switching (Claude → GPT → Gemini)
+destroys KV cache at every boundary.
+No cross-provider cache sharing.
+MCP→Agent API migration reduces
+schema bloat but doesn't fix model switching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Primary Cache Invalidation Risk</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HIGH:
+• Changing timestamps in prompts
+• Dynamic metadata injection
+• Tool result variations
+• Model switching mid-session
+• Adding/removing skills
+• Group chat context changes
+Root cause: dynamic content placed
+before static content in prompt.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MODERATE:
+• Changing system prompt casing
+• Adding timestamps at prompt start
+• Adding/removing MCP tools
+• Switching models mid-session
+Mitigated by strict ordering:
+tools → system → messages.
+Static prefix design principle.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>STRUCTURAL:
+• Every model switch = full cache miss
+• 19 models = up to 19 separate caches
+• Sub-agents don't share KV state
+• Provider-side caching is per-model
+The architecture fundamentally trades
+cache efficiency for model specialization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cache Optimization Strategy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1. ContextEngine plugin (2026.3.7):
+   7 lifecycle hooks for custom logic
+2. Reorder prompt: static prefix first,
+   dynamic content at end
+3. Isolated Mode for cron jobs:
+   eliminates history carryover
+4. Pre-send token estimation for
+   proactive compaction
+5. Local inference: PagedAttention +
+   prefix caching via vLLM/SGLang</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1. Prompt caching with byte-exact
+   prefix matching (5-min TTL)
+2. Cache hierarchy:
+   tools → system → messages
+3. Auto-compaction at ~70% utilization
+4. Sub-agent parallelism shares
+   system prompt cache
+5. 1-hour TTL option at 2× price
+   for bursty workloads</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1. Agent API replaces MCP to reduce
+   schema overhead (72% → minimal)
+2. Task decomposition: smaller,
+   model-specific calls vs monolithic
+3. Provider-side caching per model
+   (OpenAI 50%, Anthropic 90% discount)
+4. Filesystem sharing between sub-agents
+   (avoids re-fetching data)
+5. Credit system abstracts token costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COST IMPACT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caching Cost Savings</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Highly variable — depends on user's
+model provider and cache hit rate.
+With Anthropic Claude:
+  Cached: $0.30/M vs $3.00/M (90% off)
+  But low hit rate reduces savings.
+With OpenAI GPT:
+  Cached: 50% off input tokens.
+Local inference: no token cost,
+but 300s prefill on consumer GPU
+for 80K prompt if cache misses.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Highest savings due to best hit rate.
+100M tokens tracked:
+  Without caching: ~$310
+  With 84% cache: ~$82
+  Savings: $228 (74%)
+Per-request: $0.24 → $0.06 (75% cut).
+Agent teams: 97.2% hit rate ×
+4 parallel agents = near-optimal
+token efficiency per agent.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Opaque — abstracted into credits.
+$200/mo Max subscription includes
+10K credits. No per-token visibility.
+Underlying cost is HIGH because:
+  • Multi-model = minimal cross-cache
+  • Premium models (Opus, GPT-5.2)
+  • Multiple sub-calls per task
+But user sees flat credit cost,
+not raw token economics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cost of Cache Miss</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>40K system prompt cache miss:
+  Claude Sonnet: $0.12 per miss
+  vs $0.012 cached (10× penalty).
+5-turn chat: 13× single-turn cost
+due to full history re-send.
+Web fetching: 320K+ input tokens
+per request → extremely expensive
+if uncached.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>78K avg prompt cache miss:
+  Opus: $0.39 per miss
+  vs $0.039 cached (10× penalty).
+Cowork sessions burn quota faster
+than regular chat due to multi-step
+reasoning overhead.
+5-hour rate limit resets constrain
+heavy usage regardless of caching.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Every model switch is a cache miss.
+A 5-step task routed across 3 models
+= 3 full cold-start prefills.
+Estimated per-task token burn:
+  Simple task: ~5–15K tokens total
+  Complex task: ~50–200K+ tokens
+  across multiple model calls.
+Credit system shields user from
+raw cost but limits throughput.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNIQUE CHARACTERISTICS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Architectural Advantage</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ONLY platform with local inference option.
+Local: Full KV cache control —
+PagedAttention, prefix caching,
+FP8 quantization, custom eviction.
+DGX Spark: 2,851 tok/s prefill,
+128 GB unified memory.
+Model-agnostic: any provider's cache
+behavior is accessible.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BEST prompt caching in production.
+Anthropic's cache infrastructure is
+purpose-built for agent workloads.
+84–97% hit rates set the industry bar.
+Agent Teams enable parallel execution
+with shared prompt cache across
+teammates — unique capability.
+Cost reduction is automatic,
+no user tuning required.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BEST model diversity per task.
+19 specialized models means each
+sub-task gets the optimal model:
+  • Claude Opus for reasoning
+  • GPT-5.2 for long-context recall
+  • Grok for speed-critical tasks
+  • Nano Banana for images
+  • Veo 3.1 for video
+Trades cache efficiency for
+task-specific model quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Architectural Weakness</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dynamic prompt design breaks caching.
+Issues #45110, #40256 are open bugs.
+ContextEngine plugin is powerful but
+requires manual configuration.
+Consumer GPU: 4.5 tok/s prefill
+→ 300s for 80K tokens.
+Practically unusable for long context
+without datacenter hardware.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Single-provider lock-in.
+Claude family only — no model choice.
+Byte-exact matching is fragile:
+any system prompt change = full miss.
+No local inference option.
+All data flows through Anthropic cloud.
+Rate limits (5-hour resets) constrain
+heavy agent workloads.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>KV cache efficiency is structurally poor.
+Every model switch = cold start.
+19 models = 19 independent caches
+with zero cross-sharing.
+Credit system is opaque —
+no token-level cost visibility.
+No self-hosting option.
+$200/mo with 10K credit cap
+may limit heavy workloads.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>OpenClaw Input (K)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OpenClaw Cost ($)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>OpenClaw Cumul ($)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Input (K)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Cost ($)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Cumul ($)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Perplexity Input (K)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Perplexity Cost ($)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Perplexity Cumul ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.11064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="E2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06781</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="H2" t="n">
+        <v>54</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.12708</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07147000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H3" t="n">
+        <v>54</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>64</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="E4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07513</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="H4" t="n">
+        <v>54</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.585</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.15996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="E5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.07879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="H5" t="n">
+        <v>54</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7799</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="E6" t="n">
+        <v>103</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08245</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="H6" t="n">
+        <v>54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9749</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.19284</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9104</v>
+      </c>
+      <c r="E7" t="n">
+        <v>108</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08611000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="H7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.1699</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.1197</v>
+      </c>
+      <c r="E8" t="n">
+        <v>113</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08977</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.3649</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3454</v>
+      </c>
+      <c r="E9" t="n">
+        <v>118</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09343</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="H9" t="n">
+        <v>54</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.5599</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>112</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.5876</v>
+      </c>
+      <c r="E10" t="n">
+        <v>123</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.09709</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="H10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.7549</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8462</v>
+      </c>
+      <c r="E11" t="n">
+        <v>128</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.10075</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="H11" t="n">
+        <v>54</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.9498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/kv_cache_prefill_data.xlsx
+++ b/kv_cache_prefill_data.xlsx
@@ -19,8 +19,10 @@
     <sheet name="Installed Base Memory" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="KV Cache Scenarios" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Agent KV Comparison" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Multi-Turn Cost Model" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Cost Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="KV Quantization Methods" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Parameter Scaling" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Multi-Turn Cost Model" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Cost Sensitivity" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1795,379 +1797,279 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>OpenClaw Input (K)</t>
+          <t>Bits</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>OpenClaw Cost ($)</t>
+          <t>Memory Reduction</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>OpenClaw Cumul ($)</t>
+          <t>Throughput Gain</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Claude Cowork Input (K)</t>
+          <t>Accuracy Loss</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Claude Cowork Cost ($)</t>
+          <t>Training Required</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Claude Cowork Cumul ($)</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Perplexity Input (K)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Perplexity Cost ($)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Perplexity Cumul ($)</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FP16 (baseline)</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.11064</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.1106</v>
-      </c>
-      <c r="E2" t="n">
-        <v>83</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.06781</v>
+        <v>16</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0678</v>
-      </c>
-      <c r="H2" t="n">
-        <v>54</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.195</v>
+        <v>2020</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FP8</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>~1.5x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Negligible</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TensorRT-LLM, Nemotron</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KIVI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.12708</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2377</v>
-      </c>
-      <c r="E3" t="n">
-        <v>88</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.07147000000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1393</v>
-      </c>
-      <c r="H3" t="n">
-        <v>54</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2.6x (total)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.35–3.47x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Low (&lt;1 ppl)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>arXiv:2402.02750</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RotateKV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.97x</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.32x decode</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt;0.3 ppl on WikiText</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>arXiv:2501.16383</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV-Compress</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8–64x</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.18x</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>&gt;90% at 64x comp.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TurboQuant</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>64</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.14352</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="E4" t="n">
-        <v>93</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.07513</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2144</v>
-      </c>
-      <c r="H4" t="n">
-        <v>54</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.585</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>72</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.15996</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5412</v>
-      </c>
-      <c r="E5" t="n">
-        <v>98</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.07879</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2932</v>
-      </c>
-      <c r="H5" t="n">
-        <v>54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.7799</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>80</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1764</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.7176</v>
-      </c>
-      <c r="E6" t="n">
-        <v>103</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.08245</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3756</v>
-      </c>
-      <c r="H6" t="n">
-        <v>54</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9749</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>88</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.19284</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.9104</v>
-      </c>
-      <c r="E7" t="n">
-        <v>108</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.08611000000000001</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6.0x</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.0x (H100)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Zero (LongBench)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No (data-oblivious)</t>
+        </is>
       </c>
       <c r="G7" t="n">
-        <v>0.4617</v>
-      </c>
-      <c r="H7" t="n">
-        <v>54</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.1699</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>96</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.20928</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.1197</v>
-      </c>
-      <c r="E8" t="n">
-        <v>113</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.08977</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.5515</v>
-      </c>
-      <c r="H8" t="n">
-        <v>54</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.3649</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>104</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.22572</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.3454</v>
-      </c>
-      <c r="E9" t="n">
-        <v>118</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.09343</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.6449</v>
-      </c>
-      <c r="H9" t="n">
-        <v>54</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.5599</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>112</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.24216</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.5876</v>
-      </c>
-      <c r="E10" t="n">
-        <v>123</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.09709</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="H10" t="n">
-        <v>54</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.7549</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>120</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2586</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.8462</v>
-      </c>
-      <c r="E11" t="n">
-        <v>128</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.10075</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.8428</v>
-      </c>
-      <c r="H11" t="n">
-        <v>54</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.9498</v>
+        <v>2026</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Google, ICLR 2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2176,6 +2078,766 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Params (B)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Active (B)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Layers</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>KV Heads</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Head Dim</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Attention</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>KV MB/tok</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Weights FP8 (GB)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Llama 3.1 8B</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>128</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>GQA</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Llama 3.1 70B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>GQA</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="I3" t="n">
+        <v>70</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Llama 3.1 405B</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>405</v>
+      </c>
+      <c r="C4" t="n">
+        <v>405</v>
+      </c>
+      <c r="D4" t="n">
+        <v>126</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>128</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>GQA</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="I4" t="n">
+        <v>405</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Qwen3 8B</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GQA-4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Qwen3 32B</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>32</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>128</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GQA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>32</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Qwen3-235B (MoE)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>235</v>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>94</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GQA-4</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="I7" t="n">
+        <v>235</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Llama 4 Maverick (MoE)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>400</v>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>128</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>iRoPE+GQA</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="I8" t="n">
+        <v>400</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2 (MoE)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>685</v>
+      </c>
+      <c r="C9" t="n">
+        <v>37</v>
+      </c>
+      <c r="D9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MLA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Latent</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MLA</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I9" t="n">
+        <v>685</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MoE+MLA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>OpenClaw Input (K)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OpenClaw Cost ($)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>OpenClaw Cumul ($)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Input (K)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Cost ($)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Cumul ($)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Perplexity Input (K)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Perplexity Cost ($)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Perplexity Cumul ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.11064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="E2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06781</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="H2" t="n">
+        <v>54</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.12708</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07147000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H3" t="n">
+        <v>54</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>64</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="E4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07513</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="H4" t="n">
+        <v>54</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.585</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.15996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="E5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.07879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="H5" t="n">
+        <v>54</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7799</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="E6" t="n">
+        <v>103</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08245</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="H6" t="n">
+        <v>54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9749</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.19284</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9104</v>
+      </c>
+      <c r="E7" t="n">
+        <v>108</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08611000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="H7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.1699</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.1197</v>
+      </c>
+      <c r="E8" t="n">
+        <v>113</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08977</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.3649</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3454</v>
+      </c>
+      <c r="E9" t="n">
+        <v>118</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09343</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="H9" t="n">
+        <v>54</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.5599</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>112</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.5876</v>
+      </c>
+      <c r="E10" t="n">
+        <v>123</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.09709</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="H10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.7549</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8462</v>
+      </c>
+      <c r="E11" t="n">
+        <v>128</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.10075</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="H11" t="n">
+        <v>54</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.9498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/kv_cache_prefill_data.xlsx
+++ b/kv_cache_prefill_data.xlsx
@@ -21,8 +21,10 @@
     <sheet name="Agent KV Comparison" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="KV Quantization Methods" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Parameter Scaling" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Multi-Turn Cost Model" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Cost Sensitivity" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Training vs Inference Mem" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Compute Split Timeline" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Multi-Turn Cost Model" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Cost Sensitivity" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2457,379 +2459,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>OpenClaw Input (K)</t>
+          <t>Training FP16 (GB)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>OpenClaw Cost ($)</t>
+          <t>Training FP8 (GB)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>OpenClaw Cumul ($)</t>
+          <t>Inference FP16 (GB)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Claude Cowork Input (K)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Claude Cowork Cost ($)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Claude Cowork Cumul ($)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Perplexity Input (K)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Perplexity Cost ($)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Perplexity Cumul ($)</t>
+          <t>Inference FP8 (GB)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Model Weights</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>0.11064</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1106</v>
+        <v>140</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.06781</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0678</v>
-      </c>
-      <c r="H2" t="n">
-        <v>54</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.195</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gradients</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>140</v>
+      </c>
+      <c r="C3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Optimizer States (Adam)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>280</v>
+      </c>
+      <c r="C4" t="n">
+        <v>280</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Activations (batch=8, seq=4K)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.12708</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2377</v>
-      </c>
-      <c r="E3" t="n">
-        <v>88</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.07147000000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1393</v>
-      </c>
-      <c r="H3" t="n">
-        <v>54</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>64</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.14352</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="E4" t="n">
-        <v>93</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.07513</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.2144</v>
-      </c>
-      <c r="H4" t="n">
-        <v>54</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.585</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>72</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.15996</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5412</v>
-      </c>
       <c r="E5" t="n">
-        <v>98</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.07879</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2932</v>
-      </c>
-      <c r="H5" t="n">
-        <v>54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.7799</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KV Cache (1 user, 4K ctx)</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1764</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7176</v>
+        <v>1.3</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.08245</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3756</v>
-      </c>
-      <c r="H6" t="n">
-        <v>54</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9749</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KV Cache (32 users, 32K ctx)</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.19284</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9104</v>
+        <v>336</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.08611000000000001</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.4617</v>
-      </c>
-      <c r="H7" t="n">
-        <v>54</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.1699</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KV Cache (8 users, 128K ctx)</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.20928</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1197</v>
+        <v>336</v>
       </c>
       <c r="E8" t="n">
-        <v>113</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.08977</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.5515</v>
-      </c>
-      <c r="H8" t="n">
-        <v>54</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.3649</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>104</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.22572</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.3454</v>
-      </c>
-      <c r="E9" t="n">
-        <v>118</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.09343</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.6449</v>
-      </c>
-      <c r="H9" t="n">
-        <v>54</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.5599</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>112</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.24216</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.5876</v>
-      </c>
-      <c r="E10" t="n">
-        <v>123</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.09709</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="H10" t="n">
-        <v>54</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.7549</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>120</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2586</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.8462</v>
-      </c>
-      <c r="E11" t="n">
-        <v>128</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.10075</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.8428</v>
-      </c>
-      <c r="H11" t="n">
-        <v>54</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.19498</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.9498</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -2838,6 +2628,578 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Training Share (%)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Inference Share (%)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Total AI Compute ($B)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Training Spend ($B)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Inference Spend ($B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B3" t="n">
+        <v>67</v>
+      </c>
+      <c r="C3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>130</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" t="n">
+        <v>67</v>
+      </c>
+      <c r="D6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E6" t="n">
+        <v>99</v>
+      </c>
+      <c r="F6" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n">
+        <v>72</v>
+      </c>
+      <c r="D7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E7" t="n">
+        <v>112</v>
+      </c>
+      <c r="F7" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" t="n">
+        <v>125</v>
+      </c>
+      <c r="F8" t="n">
+        <v>375</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>OpenClaw Input (K)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>OpenClaw Cost ($)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>OpenClaw Cumul ($)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Input (K)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Cost ($)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Claude Cowork Cumul ($)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Perplexity Input (K)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Perplexity Cost ($)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Perplexity Cumul ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.11064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="E2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06781</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0678</v>
+      </c>
+      <c r="H2" t="n">
+        <v>54</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.12708</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07147000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="H3" t="n">
+        <v>54</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>64</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="E4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07513</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="H4" t="n">
+        <v>54</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.585</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.15996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="E5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.07879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="H5" t="n">
+        <v>54</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7799</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="E6" t="n">
+        <v>103</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08245</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="H6" t="n">
+        <v>54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9749</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.19284</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9104</v>
+      </c>
+      <c r="E7" t="n">
+        <v>108</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08611000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="H7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.1699</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.1197</v>
+      </c>
+      <c r="E8" t="n">
+        <v>113</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08977</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.3649</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3454</v>
+      </c>
+      <c r="E9" t="n">
+        <v>118</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09343</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="H9" t="n">
+        <v>54</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.5599</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>112</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.5876</v>
+      </c>
+      <c r="E10" t="n">
+        <v>123</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.09709</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="H10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.7549</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8462</v>
+      </c>
+      <c r="E11" t="n">
+        <v>128</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.10075</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="H11" t="n">
+        <v>54</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.19498</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.9498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
